--- a/results_(stress_test)_original/cnn_evaluation(stress_test)_pcc_origin.xlsx
+++ b/results_(stress_test)_original/cnn_evaluation(stress_test)_pcc_origin.xlsx
@@ -7,8 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="nrr_0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="nrr_0.75" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="nrn_62" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="nrn_32" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="nrn_16" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="nrn_8" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="nrn_4" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,16 +466,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57.76031434184676</v>
+        <v>89.43952802359881</v>
       </c>
       <c r="C2" t="n">
-        <v>54.25055885430815</v>
+        <v>87.33608517933283</v>
       </c>
       <c r="D2" t="n">
-        <v>1.29604559019208</v>
+        <v>0.3722499389630684</v>
       </c>
       <c r="E2" t="n">
-        <v>57.76031434184677</v>
+        <v>89.43952802359883</v>
       </c>
     </row>
     <row r="3">
@@ -482,16 +485,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.32809430255403</v>
+        <v>94.77876106194689</v>
       </c>
       <c r="C3" t="n">
-        <v>32.50527016960993</v>
+        <v>94.3358506603571</v>
       </c>
       <c r="D3" t="n">
-        <v>3.244502687826753</v>
+        <v>0.2025917836955387</v>
       </c>
       <c r="E3" t="n">
-        <v>37.32809430255403</v>
+        <v>94.77876106194689</v>
       </c>
     </row>
     <row r="4">
@@ -501,16 +504,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.72691552062868</v>
+        <v>88.73156342182891</v>
       </c>
       <c r="C4" t="n">
-        <v>68.06592476609666</v>
+        <v>87.29729169965887</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8408225160092115</v>
+        <v>0.3996818203263501</v>
       </c>
       <c r="E4" t="n">
-        <v>70.72691552062868</v>
+        <v>88.73156342182891</v>
       </c>
     </row>
     <row r="5">
@@ -520,16 +523,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.08055009823183</v>
+        <v>91.12094395280236</v>
       </c>
       <c r="C5" t="n">
-        <v>50.49650134227976</v>
+        <v>90.90185675712696</v>
       </c>
       <c r="D5" t="n">
-        <v>1.362848997116089</v>
+        <v>0.2354181815792496</v>
       </c>
       <c r="E5" t="n">
-        <v>51.08055009823183</v>
+        <v>91.12094395280236</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +542,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.46758349705304</v>
+        <v>95.6047197640118</v>
       </c>
       <c r="C6" t="n">
-        <v>67.8841305788508</v>
+        <v>95.54964892735664</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9053588919341564</v>
+        <v>0.1130508669545331</v>
       </c>
       <c r="E6" t="n">
-        <v>68.46758349705304</v>
+        <v>95.6047197640118</v>
       </c>
     </row>
     <row r="7">
@@ -558,16 +561,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.74066797642436</v>
+        <v>89.97102051055805</v>
       </c>
       <c r="C7" t="n">
-        <v>43.85106812868059</v>
+        <v>89.76571335158417</v>
       </c>
       <c r="D7" t="n">
-        <v>1.436137974262238</v>
+        <v>0.242820315452991</v>
       </c>
       <c r="E7" t="n">
-        <v>47.74066797642436</v>
+        <v>89.97102051055806</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +580,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63.45776031434185</v>
+        <v>93.42182890855457</v>
       </c>
       <c r="C8" t="n">
-        <v>62.41057353369774</v>
+        <v>93.06936155388841</v>
       </c>
       <c r="D8" t="n">
-        <v>1.109570725762751</v>
+        <v>0.1785258585996862</v>
       </c>
       <c r="E8" t="n">
-        <v>63.45776031434185</v>
+        <v>93.42182890855456</v>
       </c>
     </row>
     <row r="9">
@@ -596,16 +599,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67.77996070726915</v>
+        <v>96.22418879056048</v>
       </c>
       <c r="C9" t="n">
-        <v>66.64464578048776</v>
+        <v>96.15464939639176</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9541083838266786</v>
+        <v>0.09259862891399991</v>
       </c>
       <c r="E9" t="n">
-        <v>67.77996070726915</v>
+        <v>96.22418879056048</v>
       </c>
     </row>
     <row r="10">
@@ -615,16 +618,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81.82711198428291</v>
+        <v>98.52507374631269</v>
       </c>
       <c r="C10" t="n">
-        <v>81.52791583514156</v>
+        <v>98.52172052400064</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4541543209925294</v>
+        <v>0.04412239807681241</v>
       </c>
       <c r="E10" t="n">
-        <v>81.82711198428291</v>
+        <v>98.52507374631269</v>
       </c>
     </row>
     <row r="11">
@@ -634,16 +637,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66.30648330058939</v>
+        <v>94.92625368731564</v>
       </c>
       <c r="C11" t="n">
-        <v>65.46436297291208</v>
+        <v>94.76976439666782</v>
       </c>
       <c r="D11" t="n">
-        <v>1.065741023048759</v>
+        <v>0.1346916495242567</v>
       </c>
       <c r="E11" t="n">
-        <v>66.30648330058939</v>
+        <v>94.92625368731564</v>
       </c>
     </row>
     <row r="12">
@@ -653,16 +656,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76.62082514734774</v>
+        <v>89.58702064896755</v>
       </c>
       <c r="C12" t="n">
-        <v>76.32265193683652</v>
+        <v>88.78077064743205</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6881288235308602</v>
+        <v>0.304442451086652</v>
       </c>
       <c r="E12" t="n">
-        <v>76.62082514734774</v>
+        <v>89.58702064896755</v>
       </c>
     </row>
     <row r="13">
@@ -672,16 +675,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61.59135559921415</v>
+        <v>95.54572271386431</v>
       </c>
       <c r="C13" t="n">
-        <v>61.58620208505297</v>
+        <v>95.44795235296249</v>
       </c>
       <c r="D13" t="n">
-        <v>1.228552758693695</v>
+        <v>0.1186625673638143</v>
       </c>
       <c r="E13" t="n">
-        <v>61.59135559921415</v>
+        <v>95.54572271386431</v>
       </c>
     </row>
     <row r="14">
@@ -691,16 +694,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57.66208251473478</v>
+        <v>90.85545722713864</v>
       </c>
       <c r="C14" t="n">
-        <v>53.62886588770217</v>
+        <v>90.2721661293351</v>
       </c>
       <c r="D14" t="n">
-        <v>1.201799985021353</v>
+        <v>0.266475647980648</v>
       </c>
       <c r="E14" t="n">
-        <v>57.66208251473477</v>
+        <v>90.85545722713864</v>
       </c>
     </row>
     <row r="15">
@@ -710,16 +713,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55.69744597249509</v>
+        <v>90.80182354518638</v>
       </c>
       <c r="C15" t="n">
-        <v>50.43441243608706</v>
+        <v>90.77161624065944</v>
       </c>
       <c r="D15" t="n">
-        <v>1.457954740151763</v>
+        <v>0.2360119729690874</v>
       </c>
       <c r="E15" t="n">
-        <v>55.69744597249509</v>
+        <v>90.80182354518638</v>
       </c>
     </row>
     <row r="16">
@@ -729,16 +732,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>51.37524557956778</v>
+        <v>93.30383480825958</v>
       </c>
       <c r="C16" t="n">
-        <v>40.70378158952003</v>
+        <v>93.0688537040479</v>
       </c>
       <c r="D16" t="n">
-        <v>2.182307252660394</v>
+        <v>0.147377773468664</v>
       </c>
       <c r="E16" t="n">
-        <v>51.37524557956779</v>
+        <v>93.30383480825958</v>
       </c>
     </row>
     <row r="17">
@@ -748,16 +751,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>70.03929273084479</v>
+        <v>96.78466076696165</v>
       </c>
       <c r="C17" t="n">
-        <v>70.44934734733192</v>
+        <v>96.72399280102388</v>
       </c>
       <c r="D17" t="n">
-        <v>0.890816843137145</v>
+        <v>0.07552006294705885</v>
       </c>
       <c r="E17" t="n">
-        <v>70.03929273084479</v>
+        <v>96.78466076696165</v>
       </c>
     </row>
     <row r="18">
@@ -767,16 +770,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>66.01178781925344</v>
+        <v>93.39233038348083</v>
       </c>
       <c r="C18" t="n">
-        <v>66.08802545050354</v>
+        <v>92.2901183982168</v>
       </c>
       <c r="D18" t="n">
-        <v>1.021823577582836</v>
+        <v>0.3143563437724463</v>
       </c>
       <c r="E18" t="n">
-        <v>66.01178781925344</v>
+        <v>93.39233038348083</v>
       </c>
     </row>
     <row r="19">
@@ -786,16 +789,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>76.81728880157171</v>
+        <v>96.57817109144543</v>
       </c>
       <c r="C19" t="n">
-        <v>75.80837776822938</v>
+        <v>96.41712829680931</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7936029334086925</v>
+        <v>0.1228001547816651</v>
       </c>
       <c r="E19" t="n">
-        <v>76.81728880157171</v>
+        <v>96.57817109144543</v>
       </c>
     </row>
     <row r="20">
@@ -805,16 +808,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63.16306483300589</v>
+        <v>94.30730369639875</v>
       </c>
       <c r="C20" t="n">
-        <v>60.37086637879953</v>
+        <v>94.1397720225942</v>
       </c>
       <c r="D20" t="n">
-        <v>1.637369228759781</v>
+        <v>0.1488307094293911</v>
       </c>
       <c r="E20" t="n">
-        <v>63.16306483300589</v>
+        <v>94.30730369639875</v>
       </c>
     </row>
     <row r="21">
@@ -824,16 +827,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>60.0196463654224</v>
+        <v>84.63178747220996</v>
       </c>
       <c r="C21" t="n">
-        <v>59.63029938161859</v>
+        <v>83.09092494827173</v>
       </c>
       <c r="D21" t="n">
-        <v>1.72074930742383</v>
+        <v>0.3889422788886198</v>
       </c>
       <c r="E21" t="n">
-        <v>60.0196463654224</v>
+        <v>84.63178747220996</v>
       </c>
     </row>
     <row r="22">
@@ -843,16 +846,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>57.26915520628684</v>
+        <v>93.5693215339233</v>
       </c>
       <c r="C22" t="n">
-        <v>49.47412238445718</v>
+        <v>92.9428484308249</v>
       </c>
       <c r="D22" t="n">
-        <v>1.452023873105645</v>
+        <v>0.180543266593304</v>
       </c>
       <c r="E22" t="n">
-        <v>57.26915520628684</v>
+        <v>93.5693215339233</v>
       </c>
     </row>
     <row r="23">
@@ -862,16 +865,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>66.99410609037328</v>
+        <v>91.76991150442477</v>
       </c>
       <c r="C23" t="n">
-        <v>66.10700954110254</v>
+        <v>91.54192439895938</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9089962504804134</v>
+        <v>0.2217416511624227</v>
       </c>
       <c r="E23" t="n">
-        <v>66.99410609037328</v>
+        <v>91.76991150442477</v>
       </c>
     </row>
     <row r="24">
@@ -881,16 +884,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>74.55795677799607</v>
+        <v>93.62849159594806</v>
       </c>
       <c r="C24" t="n">
-        <v>74.46769729544356</v>
+        <v>93.47278908970786</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5543655138462782</v>
+        <v>0.1743372997551433</v>
       </c>
       <c r="E24" t="n">
-        <v>74.55795677799607</v>
+        <v>93.62849159594806</v>
       </c>
     </row>
     <row r="25">
@@ -900,16 +903,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54.32220039292731</v>
+        <v>94.3362831858407</v>
       </c>
       <c r="C25" t="n">
-        <v>52.72503617024063</v>
+        <v>94.11392545472691</v>
       </c>
       <c r="D25" t="n">
-        <v>1.465529181063175</v>
+        <v>0.1922387210991777</v>
       </c>
       <c r="E25" t="n">
-        <v>54.32220039292731</v>
+        <v>94.3362831858407</v>
       </c>
     </row>
     <row r="26">
@@ -919,16 +922,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64.24361493123772</v>
+        <v>91.74041297935102</v>
       </c>
       <c r="C26" t="n">
-        <v>64.32606697767559</v>
+        <v>91.28769886603868</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9774309247732162</v>
+        <v>0.201026857720611</v>
       </c>
       <c r="E26" t="n">
-        <v>64.24361493123773</v>
+        <v>91.74041297935102</v>
       </c>
     </row>
     <row r="27">
@@ -938,16 +941,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>57.85854616895875</v>
+        <v>85.95870206489676</v>
       </c>
       <c r="C27" t="n">
-        <v>57.04989894817076</v>
+        <v>85.4462570823422</v>
       </c>
       <c r="D27" t="n">
-        <v>1.45373560488224</v>
+        <v>0.5075744410452444</v>
       </c>
       <c r="E27" t="n">
-        <v>57.85854616895875</v>
+        <v>85.95870206489676</v>
       </c>
     </row>
     <row r="28">
@@ -957,16 +960,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63.7524557956778</v>
+        <v>86.57817109144543</v>
       </c>
       <c r="C28" t="n">
-        <v>63.27063765532206</v>
+        <v>85.07099398449692</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9418990723788738</v>
+        <v>0.6362541699592839</v>
       </c>
       <c r="E28" t="n">
-        <v>63.7524557956778</v>
+        <v>86.57817109144543</v>
       </c>
     </row>
     <row r="29">
@@ -976,16 +979,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>83.20235756385068</v>
+        <v>99.29203539823008</v>
       </c>
       <c r="C29" t="n">
-        <v>83.22826344297454</v>
+        <v>99.29332848187049</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5641614852938801</v>
+        <v>0.02703576343175674</v>
       </c>
       <c r="E29" t="n">
-        <v>83.2023575638507</v>
+        <v>99.29203539823008</v>
       </c>
     </row>
     <row r="30">
@@ -995,16 +998,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>78.68369351669941</v>
+        <v>99.46902654867256</v>
       </c>
       <c r="C30" t="n">
-        <v>78.0426304335417</v>
+        <v>99.4704211019734</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6215937665401725</v>
+        <v>0.01330160792460724</v>
       </c>
       <c r="E30" t="n">
-        <v>78.68369351669942</v>
+        <v>99.46902654867256</v>
       </c>
     </row>
     <row r="31">
@@ -1014,16 +1017,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>87.03339882121807</v>
+        <v>94.30678466076697</v>
       </c>
       <c r="C31" t="n">
-        <v>87.04633048138848</v>
+        <v>93.21805113036957</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3471026491606608</v>
+        <v>0.1889710906240149</v>
       </c>
       <c r="E31" t="n">
-        <v>87.03339882121807</v>
+        <v>94.30678466076697</v>
       </c>
     </row>
     <row r="32">
@@ -1033,16 +1036,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64.64636542239685</v>
+        <v>92.97270449283009</v>
       </c>
       <c r="C32" t="n">
-        <v>62.79538251846879</v>
+        <v>92.48544920030095</v>
       </c>
       <c r="D32" t="n">
-        <v>1.159307829428872</v>
+        <v>0.2160732091363366</v>
       </c>
       <c r="E32" t="n">
-        <v>64.64636542239685</v>
+        <v>92.97270449283009</v>
       </c>
     </row>
     <row r="33">
@@ -1052,16 +1055,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11.01366291482582</v>
+        <v>3.672319141012739</v>
       </c>
       <c r="C33" t="n">
-        <v>12.63729490288149</v>
+        <v>4.054220959590976</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5601257795600448</v>
+        <v>0.1370219992838098</v>
       </c>
       <c r="E33" t="n">
-        <v>11.01366291482582</v>
+        <v>3.672319141012738</v>
       </c>
     </row>
   </sheetData>
@@ -1112,16 +1115,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.90373280943025</v>
+        <v>90.32448377581122</v>
       </c>
       <c r="C2" t="n">
-        <v>57.10315670431937</v>
+        <v>89.13881229667409</v>
       </c>
       <c r="D2" t="n">
-        <v>1.418666880577803</v>
+        <v>0.3141019713173591</v>
       </c>
       <c r="E2" t="n">
-        <v>60.90373280943025</v>
+        <v>90.32448377581122</v>
       </c>
     </row>
     <row r="3">
@@ -1131,16 +1134,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46.16895874263261</v>
+        <v>94.48377581120944</v>
       </c>
       <c r="C3" t="n">
-        <v>44.49197774019783</v>
+        <v>94.22570331556724</v>
       </c>
       <c r="D3" t="n">
-        <v>1.937150508165359</v>
+        <v>0.1749260015383091</v>
       </c>
       <c r="E3" t="n">
-        <v>46.16895874263262</v>
+        <v>94.48377581120944</v>
       </c>
     </row>
     <row r="4">
@@ -1150,16 +1153,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68.95874263261297</v>
+        <v>89.32153392330383</v>
       </c>
       <c r="C4" t="n">
-        <v>67.09933199913864</v>
+        <v>88.60179711725708</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8537336941808462</v>
+        <v>0.3465644956033506</v>
       </c>
       <c r="E4" t="n">
-        <v>68.95874263261297</v>
+        <v>89.32153392330383</v>
       </c>
     </row>
     <row r="5">
@@ -1169,16 +1172,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.35756385068763</v>
+        <v>91.47492625368731</v>
       </c>
       <c r="C5" t="n">
-        <v>52.63318970861162</v>
+        <v>91.1714562593007</v>
       </c>
       <c r="D5" t="n">
-        <v>1.541498966515064</v>
+        <v>0.2694040335558384</v>
       </c>
       <c r="E5" t="n">
-        <v>52.35756385068763</v>
+        <v>91.47492625368731</v>
       </c>
     </row>
     <row r="6">
@@ -1188,16 +1191,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.77013752455796</v>
+        <v>95.57522123893804</v>
       </c>
       <c r="C6" t="n">
-        <v>58.68181560373077</v>
+        <v>95.50761805609457</v>
       </c>
       <c r="D6" t="n">
-        <v>1.252766007557511</v>
+        <v>0.1354831058216708</v>
       </c>
       <c r="E6" t="n">
-        <v>62.77013752455795</v>
+        <v>95.57522123893804</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1210,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49.41060903732809</v>
+        <v>94.92625368731564</v>
       </c>
       <c r="C7" t="n">
-        <v>49.74751425543747</v>
+        <v>94.91053878397095</v>
       </c>
       <c r="D7" t="n">
-        <v>1.526189483702183</v>
+        <v>0.1414816563486966</v>
       </c>
       <c r="E7" t="n">
-        <v>49.41060903732809</v>
+        <v>94.92625368731564</v>
       </c>
     </row>
     <row r="8">
@@ -1226,16 +1229,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56.97445972495088</v>
+        <v>92.38938053097345</v>
       </c>
       <c r="C8" t="n">
-        <v>52.66842086940834</v>
+        <v>91.9645826021881</v>
       </c>
       <c r="D8" t="n">
-        <v>1.341898132057395</v>
+        <v>0.1906558892331077</v>
       </c>
       <c r="E8" t="n">
-        <v>56.97445972495089</v>
+        <v>92.38938053097345</v>
       </c>
     </row>
     <row r="9">
@@ -1245,16 +1248,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.8074656188605</v>
+        <v>97.1386430678466</v>
       </c>
       <c r="C9" t="n">
-        <v>71.22682112325876</v>
+        <v>97.0956030026847</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7815350019227481</v>
+        <v>0.07549515002195335</v>
       </c>
       <c r="E9" t="n">
-        <v>71.8074656188605</v>
+        <v>97.1386430678466</v>
       </c>
     </row>
     <row r="10">
@@ -1264,16 +1267,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81.9253438113949</v>
+        <v>98.08259587020649</v>
       </c>
       <c r="C10" t="n">
-        <v>81.64012863113267</v>
+        <v>98.08692827181316</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5400875178165734</v>
+        <v>0.05029331074739881</v>
       </c>
       <c r="E10" t="n">
-        <v>81.9253438113949</v>
+        <v>98.08259587020649</v>
       </c>
     </row>
     <row r="11">
@@ -1283,16 +1286,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>75.44204322200393</v>
+        <v>95.39823008849558</v>
       </c>
       <c r="C11" t="n">
-        <v>75.5642815257937</v>
+        <v>95.24489374580315</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7087848437950015</v>
+        <v>0.1182013747038492</v>
       </c>
       <c r="E11" t="n">
-        <v>75.44204322200393</v>
+        <v>95.39823008849558</v>
       </c>
     </row>
     <row r="12">
@@ -1302,16 +1305,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81.72888015717092</v>
+        <v>89.76435782316456</v>
       </c>
       <c r="C12" t="n">
-        <v>81.91754553779369</v>
+        <v>88.7605694271777</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7147020335542038</v>
+        <v>0.3373989183046433</v>
       </c>
       <c r="E12" t="n">
-        <v>81.72888015717092</v>
+        <v>89.76435782316456</v>
       </c>
     </row>
     <row r="13">
@@ -1321,16 +1324,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65.32416502946955</v>
+        <v>93.68731563421829</v>
       </c>
       <c r="C13" t="n">
-        <v>64.35540046923516</v>
+        <v>93.36647867586808</v>
       </c>
       <c r="D13" t="n">
-        <v>1.290623341221362</v>
+        <v>0.1909393260556196</v>
       </c>
       <c r="E13" t="n">
-        <v>65.32416502946955</v>
+        <v>93.68731563421829</v>
       </c>
     </row>
     <row r="14">
@@ -1340,16 +1343,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55.50098231827112</v>
+        <v>88.55457227138643</v>
       </c>
       <c r="C14" t="n">
-        <v>52.52598393259398</v>
+        <v>87.35702472627824</v>
       </c>
       <c r="D14" t="n">
-        <v>1.339802892878652</v>
+        <v>0.5166203977983969</v>
       </c>
       <c r="E14" t="n">
-        <v>55.50098231827112</v>
+        <v>88.55457227138643</v>
       </c>
     </row>
     <row r="15">
@@ -1359,16 +1362,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57.46561886051081</v>
+        <v>89.91150442477877</v>
       </c>
       <c r="C15" t="n">
-        <v>50.20164838545597</v>
+        <v>89.80468987453636</v>
       </c>
       <c r="D15" t="n">
-        <v>1.557451982051134</v>
+        <v>0.2837800376359761</v>
       </c>
       <c r="E15" t="n">
-        <v>57.4656188605108</v>
+        <v>89.91150442477877</v>
       </c>
     </row>
     <row r="16">
@@ -1378,16 +1381,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54.81335952848723</v>
+        <v>90.58997050147494</v>
       </c>
       <c r="C16" t="n">
-        <v>50.28408902493916</v>
+        <v>89.92400146951482</v>
       </c>
       <c r="D16" t="n">
-        <v>1.517363004386425</v>
+        <v>0.249138655748781</v>
       </c>
       <c r="E16" t="n">
-        <v>54.81335952848723</v>
+        <v>90.58997050147494</v>
       </c>
     </row>
     <row r="17">
@@ -1397,16 +1400,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>69.64636542239685</v>
+        <v>94.92625368731564</v>
       </c>
       <c r="C17" t="n">
-        <v>69.65773133266573</v>
+        <v>94.86492486505456</v>
       </c>
       <c r="D17" t="n">
-        <v>1.016184490174055</v>
+        <v>0.1249760195093889</v>
       </c>
       <c r="E17" t="n">
-        <v>69.64636542239685</v>
+        <v>94.92625368731564</v>
       </c>
     </row>
     <row r="18">
@@ -1416,16 +1419,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72.00392927308448</v>
+        <v>95.30973451327434</v>
       </c>
       <c r="C18" t="n">
-        <v>71.14553760365845</v>
+        <v>95.02134004982518</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8638520557433367</v>
+        <v>0.16791371347014</v>
       </c>
       <c r="E18" t="n">
-        <v>72.00392927308448</v>
+        <v>95.30973451327434</v>
       </c>
     </row>
     <row r="19">
@@ -1435,16 +1438,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>82.61296660117878</v>
+        <v>95.51622418879056</v>
       </c>
       <c r="C19" t="n">
-        <v>82.51092819048712</v>
+        <v>95.00047545880685</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5990191865712404</v>
+        <v>0.1530297481054731</v>
       </c>
       <c r="E19" t="n">
-        <v>82.61296660117878</v>
+        <v>95.51622418879056</v>
       </c>
     </row>
     <row r="20">
@@ -1454,16 +1457,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>68.95874263261297</v>
+        <v>92.53687315634218</v>
       </c>
       <c r="C20" t="n">
-        <v>68.76844256227005</v>
+        <v>92.24293527423757</v>
       </c>
       <c r="D20" t="n">
-        <v>1.243079596897587</v>
+        <v>0.2362435583165886</v>
       </c>
       <c r="E20" t="n">
-        <v>68.95874263261297</v>
+        <v>92.53687315634218</v>
       </c>
     </row>
     <row r="21">
@@ -1473,16 +1476,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.69744597249509</v>
+        <v>83.98230088495575</v>
       </c>
       <c r="C21" t="n">
-        <v>53.80215062707918</v>
+        <v>82.91660242172722</v>
       </c>
       <c r="D21" t="n">
-        <v>1.83155307546258</v>
+        <v>0.4021893235961518</v>
       </c>
       <c r="E21" t="n">
-        <v>55.69744597249509</v>
+        <v>83.98230088495575</v>
       </c>
     </row>
     <row r="22">
@@ -1492,16 +1495,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>68.17288801571709</v>
+        <v>94.3952802359882</v>
       </c>
       <c r="C22" t="n">
-        <v>67.7715611319061</v>
+        <v>94.34684054957759</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7713428474962711</v>
+        <v>0.1409761906378359</v>
       </c>
       <c r="E22" t="n">
-        <v>68.17288801571709</v>
+        <v>94.3952802359882</v>
       </c>
     </row>
     <row r="23">
@@ -1511,16 +1514,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52.65225933202358</v>
+        <v>92.53687315634218</v>
       </c>
       <c r="C23" t="n">
-        <v>41.23596348464638</v>
+        <v>92.33552702533174</v>
       </c>
       <c r="D23" t="n">
-        <v>2.697164673358202</v>
+        <v>0.2146319191605774</v>
       </c>
       <c r="E23" t="n">
-        <v>52.65225933202358</v>
+        <v>92.53687315634218</v>
       </c>
     </row>
     <row r="24">
@@ -1530,16 +1533,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>79.46954813359528</v>
+        <v>93.27433628318583</v>
       </c>
       <c r="C24" t="n">
-        <v>79.53907701610969</v>
+        <v>92.9420322064331</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4866442531347275</v>
+        <v>0.1831304623432516</v>
       </c>
       <c r="E24" t="n">
-        <v>79.46954813359528</v>
+        <v>93.27433628318583</v>
       </c>
     </row>
     <row r="25">
@@ -1549,16 +1552,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65.22593320235757</v>
+        <v>92.97935103244838</v>
       </c>
       <c r="C25" t="n">
-        <v>65.30667471983605</v>
+        <v>92.34767773492464</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9851115215569735</v>
+        <v>0.2303960412611559</v>
       </c>
       <c r="E25" t="n">
-        <v>65.22593320235757</v>
+        <v>92.97935103244838</v>
       </c>
     </row>
     <row r="26">
@@ -1568,16 +1571,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>66.69941060903733</v>
+        <v>91.15061548975338</v>
       </c>
       <c r="C26" t="n">
-        <v>66.29261751151411</v>
+        <v>90.19318561901108</v>
       </c>
       <c r="D26" t="n">
-        <v>1.356148054823279</v>
+        <v>0.249552834019058</v>
       </c>
       <c r="E26" t="n">
-        <v>66.69941060903733</v>
+        <v>91.15061548975336</v>
       </c>
     </row>
     <row r="27">
@@ -1587,16 +1590,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>62.67190569744597</v>
+        <v>83.59882005899705</v>
       </c>
       <c r="C27" t="n">
-        <v>62.7012511883275</v>
+        <v>83.16369978281269</v>
       </c>
       <c r="D27" t="n">
-        <v>1.002333259209991</v>
+        <v>0.6093889449318642</v>
       </c>
       <c r="E27" t="n">
-        <v>62.67190569744597</v>
+        <v>83.59882005899705</v>
       </c>
     </row>
     <row r="28">
@@ -1606,16 +1609,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54.51866404715128</v>
+        <v>85.75221238938053</v>
       </c>
       <c r="C28" t="n">
-        <v>54.12295333195605</v>
+        <v>83.91249232999141</v>
       </c>
       <c r="D28" t="n">
-        <v>1.227198425680399</v>
+        <v>0.6873964399215765</v>
       </c>
       <c r="E28" t="n">
-        <v>54.51866404715128</v>
+        <v>85.75221238938053</v>
       </c>
     </row>
     <row r="29">
@@ -1625,16 +1628,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>92.63261296660117</v>
+        <v>98.90855457227138</v>
       </c>
       <c r="C29" t="n">
-        <v>92.65162295444796</v>
+        <v>98.90622917738752</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1952481417683885</v>
+        <v>0.03438535893303651</v>
       </c>
       <c r="E29" t="n">
-        <v>92.63261296660119</v>
+        <v>98.90855457227138</v>
       </c>
     </row>
     <row r="30">
@@ -1644,16 +1647,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>80.6483300589391</v>
+        <v>99.29203539823008</v>
       </c>
       <c r="C30" t="n">
-        <v>80.21233254903629</v>
+        <v>99.29549011498256</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5743807649341761</v>
+        <v>0.02140319538626916</v>
       </c>
       <c r="E30" t="n">
-        <v>80.6483300589391</v>
+        <v>99.29203539823008</v>
       </c>
     </row>
     <row r="31">
@@ -1663,16 +1666,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>94.00785854616896</v>
+        <v>93.92330383480825</v>
       </c>
       <c r="C31" t="n">
-        <v>94.01739908167505</v>
+        <v>92.91058886545147</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1544691099261399</v>
+        <v>0.2304430228411392</v>
       </c>
       <c r="E31" t="n">
-        <v>94.00785854616896</v>
+        <v>93.92330383480825</v>
       </c>
     </row>
     <row r="32">
@@ -1682,16 +1685,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>66.90569744597251</v>
+        <v>92.65685112616316</v>
       </c>
       <c r="C32" t="n">
-        <v>65.32925162655543</v>
+        <v>92.18535797000946</v>
       </c>
       <c r="D32" t="n">
-        <v>1.110866124903987</v>
+        <v>0.2360180365622819</v>
       </c>
       <c r="E32" t="n">
-        <v>66.90569744597251</v>
+        <v>92.65685112616316</v>
       </c>
     </row>
     <row r="33">
@@ -1701,16 +1704,1963 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12.30988513720681</v>
+        <v>3.855714012695696</v>
       </c>
       <c r="C33" t="n">
-        <v>13.68646243989365</v>
+        <v>4.186283324241247</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5325907685603548</v>
+        <v>0.1533813601961018</v>
       </c>
       <c r="E33" t="n">
-        <v>12.30988513720681</v>
+        <v>3.855714012695696</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>87.52229690568257</v>
+      </c>
+      <c r="C2" t="n">
+        <v>86.75650403882665</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3891075022882433</v>
+      </c>
+      <c r="E2" t="n">
+        <v>87.52229690568257</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>93.00884955752213</v>
+      </c>
+      <c r="C3" t="n">
+        <v>92.520805383888</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2747914146845384</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93.00884955752213</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>88.79056047197641</v>
+      </c>
+      <c r="C4" t="n">
+        <v>88.04957057669847</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3193191198140994</v>
+      </c>
+      <c r="E4" t="n">
+        <v>88.79056047197641</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>90.2958503101238</v>
+      </c>
+      <c r="C5" t="n">
+        <v>90.29510631367155</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2820163402240723</v>
+      </c>
+      <c r="E5" t="n">
+        <v>90.2958503101238</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>93.92330383480825</v>
+      </c>
+      <c r="C6" t="n">
+        <v>93.48833472158816</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2143476436962373</v>
+      </c>
+      <c r="E6" t="n">
+        <v>93.92330383480825</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>88.70206489675516</v>
+      </c>
+      <c r="C7" t="n">
+        <v>88.60781535329583</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2991640829985651</v>
+      </c>
+      <c r="E7" t="n">
+        <v>88.70206489675516</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>88.82732549589529</v>
+      </c>
+      <c r="C8" t="n">
+        <v>87.62566154066511</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3381134738787106</v>
+      </c>
+      <c r="E8" t="n">
+        <v>88.82732549589529</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>90.36488204915267</v>
+      </c>
+      <c r="C9" t="n">
+        <v>89.84672506436976</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2077082053966782</v>
+      </c>
+      <c r="E9" t="n">
+        <v>90.36488204915267</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>96.34218289085545</v>
+      </c>
+      <c r="C10" t="n">
+        <v>96.18841077094083</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.107820100279802</v>
+      </c>
+      <c r="E10" t="n">
+        <v>96.34218289085545</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>93.48099897057934</v>
+      </c>
+      <c r="C11" t="n">
+        <v>93.12540249722215</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1806650262926297</v>
+      </c>
+      <c r="E11" t="n">
+        <v>93.48099897057934</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>90.17699115044248</v>
+      </c>
+      <c r="C12" t="n">
+        <v>89.81637608555916</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2930178353308293</v>
+      </c>
+      <c r="E12" t="n">
+        <v>90.17699115044248</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>94.04129793510324</v>
+      </c>
+      <c r="C13" t="n">
+        <v>93.82789711616927</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1880225903112053</v>
+      </c>
+      <c r="E13" t="n">
+        <v>94.04129793510324</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>88.55457227138643</v>
+      </c>
+      <c r="C14" t="n">
+        <v>86.95097859460087</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.372176025789425</v>
+      </c>
+      <c r="E14" t="n">
+        <v>88.55457227138643</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>86.1358662272165</v>
+      </c>
+      <c r="C15" t="n">
+        <v>85.53276906153935</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3606866241665557</v>
+      </c>
+      <c r="E15" t="n">
+        <v>86.1358662272165</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>91.50477080251559</v>
+      </c>
+      <c r="C16" t="n">
+        <v>91.26225424337773</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2375939688412473</v>
+      </c>
+      <c r="E16" t="n">
+        <v>91.50477080251559</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>89.97050147492625</v>
+      </c>
+      <c r="C17" t="n">
+        <v>89.63448692774769</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2795061404613686</v>
+      </c>
+      <c r="E17" t="n">
+        <v>89.97050147492625</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>93.15686121852265</v>
+      </c>
+      <c r="C18" t="n">
+        <v>92.73914715003384</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2155844539451816</v>
+      </c>
+      <c r="E18" t="n">
+        <v>93.15686121852265</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>95.60471976401179</v>
+      </c>
+      <c r="C19" t="n">
+        <v>95.30597902626316</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1259740272159737</v>
+      </c>
+      <c r="E19" t="n">
+        <v>95.6047197640118</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>90.73746312684366</v>
+      </c>
+      <c r="C20" t="n">
+        <v>90.19616131823076</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2796162080081558</v>
+      </c>
+      <c r="E20" t="n">
+        <v>90.73746312684366</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>77.93960155364667</v>
+      </c>
+      <c r="C21" t="n">
+        <v>76.27000453030341</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7072650084912311</v>
+      </c>
+      <c r="E21" t="n">
+        <v>77.93960155364665</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>91.65226342788432</v>
+      </c>
+      <c r="C22" t="n">
+        <v>91.50300765129145</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.2328439897314335</v>
+      </c>
+      <c r="E22" t="n">
+        <v>91.65226342788432</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>91.15148054913971</v>
+      </c>
+      <c r="C23" t="n">
+        <v>91.15877311641283</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.261174160092196</v>
+      </c>
+      <c r="E23" t="n">
+        <v>91.15148054913969</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>92.41887905604719</v>
+      </c>
+      <c r="C24" t="n">
+        <v>92.03661792950537</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.2261809733431922</v>
+      </c>
+      <c r="E24" t="n">
+        <v>92.41887905604719</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>88.37758112094396</v>
+      </c>
+      <c r="C25" t="n">
+        <v>87.79082377405783</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.4303809024706425</v>
+      </c>
+      <c r="E25" t="n">
+        <v>88.37758112094396</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>88.08259587020649</v>
+      </c>
+      <c r="C26" t="n">
+        <v>86.52252698865013</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4533590178844558</v>
+      </c>
+      <c r="E26" t="n">
+        <v>88.08259587020649</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>82.0353982300885</v>
+      </c>
+      <c r="C27" t="n">
+        <v>81.2123436202714</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.6680626277149713</v>
+      </c>
+      <c r="E27" t="n">
+        <v>82.03539823008849</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>86.57834410332269</v>
+      </c>
+      <c r="C28" t="n">
+        <v>84.85762456274468</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5455196973867714</v>
+      </c>
+      <c r="E28" t="n">
+        <v>86.57834410332269</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>97.84660766961652</v>
+      </c>
+      <c r="C29" t="n">
+        <v>97.82916269403503</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.06260481639234663</v>
+      </c>
+      <c r="E29" t="n">
+        <v>97.84660766961652</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>97.52212389380531</v>
+      </c>
+      <c r="C30" t="n">
+        <v>97.53046063204518</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0587054159704015</v>
+      </c>
+      <c r="E30" t="n">
+        <v>97.52212389380531</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>93.6283185840708</v>
+      </c>
+      <c r="C31" t="n">
+        <v>92.9991069366029</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2054544608572151</v>
+      </c>
+      <c r="E31" t="n">
+        <v>93.6283185840708</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>90.61248511376972</v>
+      </c>
+      <c r="C32" t="n">
+        <v>90.04936127402028</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.2938927284652791</v>
+      </c>
+      <c r="E32" t="n">
+        <v>90.61248511376972</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4.171785330938891</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4.523224695432099</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1502635086941152</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.171785330938894</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>79.21132535748579</v>
+      </c>
+      <c r="C2" t="n">
+        <v>79.13253590873239</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5240417782527704</v>
+      </c>
+      <c r="E2" t="n">
+        <v>79.21132535748579</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>80.55398403100374</v>
+      </c>
+      <c r="C3" t="n">
+        <v>79.91397917812579</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5741790392746527</v>
+      </c>
+      <c r="E3" t="n">
+        <v>80.55398403100374</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>79.07888476543914</v>
+      </c>
+      <c r="C4" t="n">
+        <v>78.60171135684678</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5909986760273266</v>
+      </c>
+      <c r="E4" t="n">
+        <v>79.07888476543914</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>71.31956158790301</v>
+      </c>
+      <c r="C5" t="n">
+        <v>71.106797279207</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6450911700725556</v>
+      </c>
+      <c r="E5" t="n">
+        <v>71.31956158790301</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>72.34612756165711</v>
+      </c>
+      <c r="C6" t="n">
+        <v>72.2632885631525</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7068275317549706</v>
+      </c>
+      <c r="E6" t="n">
+        <v>72.34612756165711</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>64.45626692272424</v>
+      </c>
+      <c r="C7" t="n">
+        <v>64.56983447745772</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8306546111901602</v>
+      </c>
+      <c r="E7" t="n">
+        <v>64.45626692272424</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>78.04384120969905</v>
+      </c>
+      <c r="C8" t="n">
+        <v>77.20461317412745</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.509281891406863</v>
+      </c>
+      <c r="E8" t="n">
+        <v>78.04384120969904</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>84.11742316110001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>83.78374798893108</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4219721458590356</v>
+      </c>
+      <c r="E9" t="n">
+        <v>84.11742316110001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>87.44556613811537</v>
+      </c>
+      <c r="C10" t="n">
+        <v>87.49220939358864</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.330219424025078</v>
+      </c>
+      <c r="E10" t="n">
+        <v>87.44556613811538</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>85.79485981712644</v>
+      </c>
+      <c r="C11" t="n">
+        <v>85.89874942059383</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3558969290461391</v>
+      </c>
+      <c r="E11" t="n">
+        <v>85.79485981712644</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>76.41259872490247</v>
+      </c>
+      <c r="C12" t="n">
+        <v>76.47593910646705</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6202673723300298</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76.41259872490247</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>83.69873441811781</v>
+      </c>
+      <c r="C13" t="n">
+        <v>82.74929348550424</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4599104334134608</v>
+      </c>
+      <c r="E13" t="n">
+        <v>83.69873441811781</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>64.55168297303609</v>
+      </c>
+      <c r="C14" t="n">
+        <v>63.59030547572809</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8482519272714854</v>
+      </c>
+      <c r="E14" t="n">
+        <v>64.55168297303609</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>69.45769427071168</v>
+      </c>
+      <c r="C15" t="n">
+        <v>68.66771135120585</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7412308345238368</v>
+      </c>
+      <c r="E15" t="n">
+        <v>69.45769427071168</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>64.09449908736235</v>
+      </c>
+      <c r="C16" t="n">
+        <v>63.40981313555801</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8562517578403155</v>
+      </c>
+      <c r="E16" t="n">
+        <v>64.09449908736235</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>82.10719815915363</v>
+      </c>
+      <c r="C17" t="n">
+        <v>81.95466468307634</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.456606510002166</v>
+      </c>
+      <c r="E17" t="n">
+        <v>82.10719815915363</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>76.6405418731996</v>
+      </c>
+      <c r="C18" t="n">
+        <v>75.62785174856742</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6668554235404979</v>
+      </c>
+      <c r="E18" t="n">
+        <v>76.6405418731996</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>85.99442901755205</v>
+      </c>
+      <c r="C19" t="n">
+        <v>85.90267052538759</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3814940916917597</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85.99442901755205</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>72.71204768207338</v>
+      </c>
+      <c r="C20" t="n">
+        <v>72.0949438218457</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6966108138828228</v>
+      </c>
+      <c r="E20" t="n">
+        <v>72.71204768207338</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>62.36688898692895</v>
+      </c>
+      <c r="C21" t="n">
+        <v>59.97915122368231</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9892859138548374</v>
+      </c>
+      <c r="E21" t="n">
+        <v>62.36688898692895</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>75.89546622375626</v>
+      </c>
+      <c r="C22" t="n">
+        <v>74.89338705396996</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6342206756273906</v>
+      </c>
+      <c r="E22" t="n">
+        <v>75.89546622375626</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>70.77050839540135</v>
+      </c>
+      <c r="C23" t="n">
+        <v>70.68264764100503</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6842256914824247</v>
+      </c>
+      <c r="E23" t="n">
+        <v>70.77050839540135</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>79.72196991323453</v>
+      </c>
+      <c r="C24" t="n">
+        <v>79.60166682401439</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5164598529770349</v>
+      </c>
+      <c r="E24" t="n">
+        <v>79.72196991323455</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>73.4134378325072</v>
+      </c>
+      <c r="C25" t="n">
+        <v>72.92054842111887</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5877480655908585</v>
+      </c>
+      <c r="E25" t="n">
+        <v>73.4134378325072</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>78.2149499563145</v>
+      </c>
+      <c r="C26" t="n">
+        <v>77.95474487406499</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5453774902348718</v>
+      </c>
+      <c r="E26" t="n">
+        <v>78.2149499563145</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>63.73394233514131</v>
+      </c>
+      <c r="C27" t="n">
+        <v>62.74514220681176</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.9724863683183989</v>
+      </c>
+      <c r="E27" t="n">
+        <v>63.73394233514131</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>75.32772774850994</v>
+      </c>
+      <c r="C28" t="n">
+        <v>74.93986722595523</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.6633949622511863</v>
+      </c>
+      <c r="E28" t="n">
+        <v>75.32772774850994</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>86.40775439233903</v>
+      </c>
+      <c r="C29" t="n">
+        <v>86.32583538824113</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3560406218282878</v>
+      </c>
+      <c r="E29" t="n">
+        <v>86.40775439233903</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>91.30502859021271</v>
+      </c>
+      <c r="C30" t="n">
+        <v>91.28136296613492</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.2497569598090195</v>
+      </c>
+      <c r="E30" t="n">
+        <v>91.30502859021271</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>91.50650092128824</v>
+      </c>
+      <c r="C31" t="n">
+        <v>90.96038294497787</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2226321294884352</v>
+      </c>
+      <c r="E31" t="n">
+        <v>91.50650092128825</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>76.89004806846656</v>
+      </c>
+      <c r="C32" t="n">
+        <v>76.42417989480266</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.587942369762289</v>
+      </c>
+      <c r="E32" t="n">
+        <v>76.89004806846656</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8.120631922289636</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8.369249003806782</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1938864939121652</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.120631922289636</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>60.48105952473637</v>
+      </c>
+      <c r="C2" t="n">
+        <v>59.78593353116835</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8948204219341278</v>
+      </c>
+      <c r="E2" t="n">
+        <v>60.48105952473637</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>61.16540800525956</v>
+      </c>
+      <c r="C3" t="n">
+        <v>60.6972410740248</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8674206515153248</v>
+      </c>
+      <c r="E3" t="n">
+        <v>61.16540800525956</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>58.94056176956548</v>
+      </c>
+      <c r="C4" t="n">
+        <v>57.75390476045649</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.024129038055738</v>
+      </c>
+      <c r="E4" t="n">
+        <v>58.94056176956548</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>44.06699019887715</v>
+      </c>
+      <c r="C5" t="n">
+        <v>40.6795238886321</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.314992298682531</v>
+      </c>
+      <c r="E5" t="n">
+        <v>44.06699019887715</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>52.08712878139085</v>
+      </c>
+      <c r="C6" t="n">
+        <v>51.45997211753335</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9965868989626566</v>
+      </c>
+      <c r="E6" t="n">
+        <v>52.08712878139085</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>49.61513507902318</v>
+      </c>
+      <c r="C7" t="n">
+        <v>48.02564591853183</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.088675905267398</v>
+      </c>
+      <c r="E7" t="n">
+        <v>49.61513507902318</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>65.8548084325989</v>
+      </c>
+      <c r="C8" t="n">
+        <v>65.89360133152593</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7376472373803457</v>
+      </c>
+      <c r="E8" t="n">
+        <v>65.8548084325989</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>62.93462746217527</v>
+      </c>
+      <c r="C9" t="n">
+        <v>62.06214640052598</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8456805005669594</v>
+      </c>
+      <c r="E9" t="n">
+        <v>62.93462746217527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>66.50221887732593</v>
+      </c>
+      <c r="C10" t="n">
+        <v>66.48145441914396</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7935970000301797</v>
+      </c>
+      <c r="E10" t="n">
+        <v>66.50221887732593</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>56.86000743951072</v>
+      </c>
+      <c r="C11" t="n">
+        <v>53.65938796497873</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.074159555137157</v>
+      </c>
+      <c r="E11" t="n">
+        <v>56.86000743951072</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>52.0031315149785</v>
+      </c>
+      <c r="C12" t="n">
+        <v>49.86375779199476</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.085204181075096</v>
+      </c>
+      <c r="E12" t="n">
+        <v>52.00313151497851</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>58.55163106947292</v>
+      </c>
+      <c r="C13" t="n">
+        <v>57.40078995750315</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.021787829200427</v>
+      </c>
+      <c r="E13" t="n">
+        <v>58.55163106947292</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>44.7435531449234</v>
+      </c>
+      <c r="C14" t="n">
+        <v>41.17891399651401</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.257960029443105</v>
+      </c>
+      <c r="E14" t="n">
+        <v>44.7435531449234</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>51.86870128634331</v>
+      </c>
+      <c r="C15" t="n">
+        <v>49.82489339927474</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.066501032312711</v>
+      </c>
+      <c r="E15" t="n">
+        <v>51.86870128634331</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>48.72464294673829</v>
+      </c>
+      <c r="C16" t="n">
+        <v>47.19196913205451</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.182144251465797</v>
+      </c>
+      <c r="E16" t="n">
+        <v>48.72464294673829</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>60.51747852490073</v>
+      </c>
+      <c r="C17" t="n">
+        <v>59.89256440921876</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9500508358081182</v>
+      </c>
+      <c r="E17" t="n">
+        <v>60.51747852490073</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>59.01893614996669</v>
+      </c>
+      <c r="C18" t="n">
+        <v>58.32316248206847</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9971463551123938</v>
+      </c>
+      <c r="E18" t="n">
+        <v>59.01893614996669</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>67.98536319518334</v>
+      </c>
+      <c r="C19" t="n">
+        <v>67.22881602265127</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7852731724580129</v>
+      </c>
+      <c r="E19" t="n">
+        <v>67.98536319518334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>52.4450903554529</v>
+      </c>
+      <c r="C20" t="n">
+        <v>49.57784380899894</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.116471703350544</v>
+      </c>
+      <c r="E20" t="n">
+        <v>52.4450903554529</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>46.57834410332269</v>
+      </c>
+      <c r="C21" t="n">
+        <v>42.77845531673849</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.417216952641805</v>
+      </c>
+      <c r="E21" t="n">
+        <v>46.57834410332269</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>59.69117379908131</v>
+      </c>
+      <c r="C22" t="n">
+        <v>59.14271200051417</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9491548781593639</v>
+      </c>
+      <c r="E22" t="n">
+        <v>59.69117379908131</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>53.5875742869748</v>
+      </c>
+      <c r="C23" t="n">
+        <v>51.3275974454231</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.027731768290202</v>
+      </c>
+      <c r="E23" t="n">
+        <v>53.5875742869748</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>50.84230832446647</v>
+      </c>
+      <c r="C24" t="n">
+        <v>48.45044620846268</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.092447104056676</v>
+      </c>
+      <c r="E24" t="n">
+        <v>50.84230832446648</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>46.59884601077864</v>
+      </c>
+      <c r="C25" t="n">
+        <v>42.73712062081192</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.247943102320035</v>
+      </c>
+      <c r="E25" t="n">
+        <v>46.59884601077864</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>63.31880033564304</v>
+      </c>
+      <c r="C26" t="n">
+        <v>62.60145722116655</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.8942668611804644</v>
+      </c>
+      <c r="E26" t="n">
+        <v>63.31880033564304</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>50.08053702886703</v>
+      </c>
+      <c r="C27" t="n">
+        <v>49.61384283304871</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.078560741742452</v>
+      </c>
+      <c r="E27" t="n">
+        <v>50.08053702886703</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>55.3850811858234</v>
+      </c>
+      <c r="C28" t="n">
+        <v>53.22519957980192</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.020714179674784</v>
+      </c>
+      <c r="E28" t="n">
+        <v>55.3850811858234</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>71.83522348809245</v>
+      </c>
+      <c r="C29" t="n">
+        <v>70.32005250548383</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7422243215764562</v>
+      </c>
+      <c r="E29" t="n">
+        <v>71.83522348809245</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>67.44357650152683</v>
+      </c>
+      <c r="C30" t="n">
+        <v>65.03001452852102</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.9241550615988672</v>
+      </c>
+      <c r="E30" t="n">
+        <v>67.44357650152683</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>83.20677514511371</v>
+      </c>
+      <c r="C31" t="n">
+        <v>82.30657054678656</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4653222091495991</v>
+      </c>
+      <c r="E31" t="n">
+        <v>83.20677514511371</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>57.43115713227045</v>
+      </c>
+      <c r="C32" t="n">
+        <v>55.8171663737853</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.9986662026049775</v>
+      </c>
+      <c r="E32" t="n">
+        <v>57.43115713227046</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8.732649374745037</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.452256849270483</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1892415083873272</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.732649374745035</v>
       </c>
     </row>
   </sheetData>
